--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T08:25:56+00:00</t>
+    <t>2026-09-14T07:00:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:00:54+00:00</t>
+    <t>2026-09-14T09:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:05:35+00:00</t>
+    <t>2026-09-14T11:50:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="399">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:50:31+00:00</t>
+    <t>2026-09-15T06:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -696,7 +696,7 @@
 </t>
   </si>
   <si>
-    <t>Diagnosecode (Codierservice); Freitext ist nicht zulässig. Codesysteme: 1. SNOMED CT, 2. Orphanet.</t>
+    <t>Diagnosecode (Codierservice); Freitext ist nicht zulässig.</t>
   </si>
   <si>
     <t>Identification of the condition, problem or diagnosis.</t>
@@ -705,13 +705,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Identification of the condition or diagnosis.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-diagnosen-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -778,9 +772,6 @@
     <t>Condition.code.coding</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Coding
 </t>
   </si>
@@ -797,13 +788,6 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
@@ -813,187 +797,6 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Condition.code.coding:snomed</t>
-  </si>
-  <si>
-    <t>snomed</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:snomed.id</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.id</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:snomed.extension</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:snomed.system</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:snomed.version</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:snomed.code</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:snomed.display</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:snomed.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:orphanet</t>
-  </si>
-  <si>
-    <t>orphanet</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:orphanet.id</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:orphanet.extension</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:orphanet.system</t>
-  </si>
-  <si>
-    <t>http://www.orpha.net/ORDO</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:orphanet.version</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:orphanet.code</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:orphanet.display</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:orphanet.userSelected</t>
-  </si>
-  <si>
     <t>Condition.code.text</t>
   </si>
   <si>
@@ -1028,6 +831,9 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Condition.code. If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -1788,10 +1594,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP65"/>
+  <dimension ref="A1:AP49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="30.765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="30.765625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.48828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1816,7 +1622,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.00390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.6015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3941,13 +3747,11 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="Y18" s="2"/>
+      <c r="Z18" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3980,30 +3784,30 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>228</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4026,13 +3830,13 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4083,7 +3887,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4107,7 +3911,7 @@
         <v>21</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>21</v>
@@ -4118,10 +3922,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4147,10 +3951,10 @@
         <v>136</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>158</v>
@@ -4194,7 +3998,7 @@
         <v>139</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>21</v>
@@ -4203,7 +4007,7 @@
         <v>140</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4227,7 +4031,7 @@
         <v>21</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>21</v>
@@ -4238,10 +4042,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4249,10 +4053,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -4264,19 +4068,19 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4313,17 +4117,19 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4344,10 +4150,10 @@
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>21</v>
@@ -4358,23 +4164,21 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -4386,19 +4190,19 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4447,13 +4251,13 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
@@ -4468,10 +4272,10 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>21</v>
@@ -4482,7 +4286,7 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>255</v>
@@ -4496,7 +4300,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
@@ -4505,18 +4309,20 @@
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4541,13 +4347,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>21</v>
+        <v>261</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4565,79 +4371,79 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>155</v>
+        <v>266</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>136</v>
+        <v>267</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4673,46 +4479,46 @@
         <v>21</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>234</v>
+        <v>273</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>21</v>
@@ -4720,10 +4526,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4731,10 +4537,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4746,26 +4552,24 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>105</v>
+        <v>276</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>264</v>
+        <v>21</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>21</v>
@@ -4807,7 +4611,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4822,19 +4626,19 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>21</v>
@@ -4842,10 +4646,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4868,16 +4672,16 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4927,7 +4731,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4942,19 +4746,19 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>21</v>
@@ -4962,10 +4766,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4973,7 +4777,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
@@ -4985,21 +4789,21 @@
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>111</v>
+        <v>285</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -5047,7 +4851,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5056,7 +4860,7 @@
         <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>103</v>
@@ -5068,24 +4872,24 @@
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>282</v>
+        <v>21</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>21</v>
+        <v>299</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5093,13 +4897,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -5108,18 +4912,16 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="N28" s="2"/>
-      <c r="O28" t="s" s="2">
-        <v>288</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -5167,7 +4969,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5188,24 +4990,24 @@
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>21</v>
+        <v>305</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5213,13 +5015,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -5228,20 +5030,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5289,7 +5087,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5310,13 +5108,13 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>300</v>
+        <v>21</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>21</v>
+        <v>311</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>21</v>
@@ -5324,14 +5122,12 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5352,20 +5148,16 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>242</v>
+        <v>313</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>243</v>
+        <v>314</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5413,13 +5205,13 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>249</v>
+        <v>312</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -5434,13 +5226,13 @@
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>250</v>
+        <v>316</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>251</v>
+        <v>317</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>21</v>
+        <v>318</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>21</v>
@@ -5448,10 +5240,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>255</v>
+        <v>319</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5462,7 +5254,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5474,13 +5266,13 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>230</v>
+        <v>320</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>231</v>
+        <v>321</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>232</v>
+        <v>322</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5531,19 +5323,19 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
@@ -5555,7 +5347,7 @@
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>234</v>
+        <v>324</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>21</v>
@@ -5566,21 +5358,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>257</v>
+        <v>325</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5592,17 +5384,15 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5639,31 +5429,31 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
@@ -5675,7 +5465,7 @@
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>21</v>
@@ -5686,21 +5476,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5709,29 +5499,27 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>307</v>
+        <v>21</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>21</v>
@@ -5773,19 +5561,19 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
@@ -5794,10 +5582,10 @@
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>266</v>
+        <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5808,44 +5596,46 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>269</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>230</v>
+        <v>136</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>270</v>
+        <v>329</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>271</v>
+        <v>330</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5893,19 +5683,19 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>273</v>
+        <v>331</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
@@ -5914,10 +5704,10 @@
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>275</v>
+        <v>134</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -5928,10 +5718,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5939,7 +5729,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>91</v>
@@ -5951,21 +5741,19 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>333</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>280</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5989,13 +5777,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>21</v>
+        <v>335</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>21</v>
+        <v>336</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -6013,7 +5801,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>281</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6022,7 +5810,7 @@
         <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>103</v>
@@ -6031,13 +5819,13 @@
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>282</v>
+        <v>181</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>283</v>
+        <v>224</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
@@ -6048,10 +5836,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>285</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6062,7 +5850,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -6071,21 +5859,19 @@
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>230</v>
+        <v>340</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>287</v>
+        <v>342</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>288</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -6133,16 +5919,16 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>103</v>
@@ -6154,10 +5940,10 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>291</v>
+        <v>343</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6168,10 +5954,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>293</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6191,23 +5977,19 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>294</v>
+        <v>171</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>295</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -6231,13 +6013,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>21</v>
+        <v>348</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -6255,7 +6037,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6276,10 +6058,10 @@
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>300</v>
+        <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>301</v>
+        <v>349</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6290,10 +6072,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6304,7 +6086,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -6313,23 +6095,21 @@
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>230</v>
+        <v>320</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6377,19 +6157,19 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>354</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>21</v>
@@ -6398,10 +6178,10 @@
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>318</v>
+        <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
@@ -6412,10 +6192,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6426,7 +6206,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -6435,20 +6215,18 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>321</v>
+        <v>229</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6473,13 +6251,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>220</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>324</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>325</v>
+        <v>21</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6497,79 +6275,79 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>320</v>
+        <v>231</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>326</v>
+        <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>330</v>
+        <v>155</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>332</v>
+        <v>234</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6617,34 +6395,34 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>329</v>
+        <v>237</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>335</v>
+        <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>337</v>
+        <v>232</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>338</v>
+        <v>21</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>21</v>
@@ -6652,44 +6430,46 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>340</v>
+        <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6737,34 +6517,34 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>345</v>
+        <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>346</v>
+        <v>134</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>21</v>
@@ -6772,10 +6552,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6786,7 +6566,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6798,17 +6578,15 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>349</v>
+        <v>171</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6833,13 +6611,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -6857,34 +6635,34 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>21</v>
@@ -6892,10 +6670,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6906,7 +6684,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
@@ -6915,20 +6693,18 @@
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6977,16 +6753,16 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>103</v>
@@ -7001,21 +6777,21 @@
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7023,28 +6799,28 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7095,13 +6871,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -7110,30 +6886,30 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7141,28 +6917,28 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>371</v>
+        <v>228</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>372</v>
+        <v>229</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>373</v>
+        <v>230</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7213,7 +6989,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>370</v>
+        <v>231</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7225,7 +7001,7 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
@@ -7237,10 +7013,10 @@
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>374</v>
+        <v>232</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>21</v>
@@ -7248,21 +7024,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -7271,18 +7047,20 @@
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>377</v>
+        <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>378</v>
+        <v>234</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7319,31 +7097,31 @@
         <v>21</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>376</v>
+        <v>237</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
@@ -7352,13 +7130,13 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>381</v>
+        <v>232</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>382</v>
+        <v>21</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>21</v>
@@ -7366,10 +7144,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7389,18 +7167,20 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7449,31 +7229,31 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
@@ -7484,10 +7264,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7498,7 +7278,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7507,16 +7287,16 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>231</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>232</v>
+        <v>390</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7567,7 +7347,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>233</v>
+        <v>391</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7579,7 +7359,7 @@
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
@@ -7588,10 +7368,10 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>234</v>
+        <v>392</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -7602,21 +7382,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7625,20 +7405,18 @@
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>136</v>
+        <v>394</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>236</v>
+        <v>395</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7687,19 +7465,19 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>239</v>
+        <v>397</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
@@ -7708,1924 +7486,20 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>234</v>
+        <v>398</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP65" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP65">
+  <autoFilter ref="A1:AP49">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9635,7 +7509,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI64">
+  <conditionalFormatting sqref="A2:AI48">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T06:30:22+00:00</t>
+    <t>2026-09-15T08:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -705,7 +705,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-diagnosen-codes</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-condition-code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1622,7 +1622,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.6015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.9140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:16:05+00:00</t>
+    <t>2026-09-16T05:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T05:34:40+00:00</t>
+    <t>2026-09-17T07:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:46:21+00:00</t>
+    <t>2026-09-17T12:50:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:50:52+00:00</t>
+    <t>2026-09-18T07:26:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:26:42+00:00</t>
+    <t>2026-09-29T15:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="465">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:00:21+00:00</t>
+    <t>2026-09-30T11:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -527,7 +527,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem.</t>
+    <t>External Ids for this condition</t>
   </si>
   <si>
     <t>Business identifiers assigned to this condition by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -539,6 +539,10 @@
     <t>Allows identification of the condition as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -548,13 +552,244 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>Condition.clinicalStatus</t>
+    <t>Condition.identifier:businessIdentifier</t>
+  </si>
+  <si>
+    <t>businessIdentifier</t>
+  </si>
+  <si>
+    <t>Identifier innerhalb der e-Diagnose für einen Eintrag.</t>
+  </si>
+  <si>
+    <t>Dieser Identifier wird von der Fachanwendung e-Diagnose vergeben, sollte dieser durch den Client nicht gesetzt werden. Ein Client kann diesen Identifier nutzen, um einzelne Einträge im Zuge einer Bearbeitung miteinander zu verknüpfen.</t>
+  </si>
+  <si>
+    <t>Condition.identifier:businessIdentifier.id</t>
+  </si>
+  <si>
+    <t>Condition.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Condition.identifier:businessIdentifier.extension</t>
+  </si>
+  <si>
+    <t>Condition.identifier.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Condition.identifier:businessIdentifier.use</t>
+  </si>
+  <si>
+    <t>Condition.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Condition.identifier:businessIdentifier.type</t>
+  </si>
+  <si>
+    <t>Condition.identifier.type</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Condition.identifier:businessIdentifier.system</t>
+  </si>
+  <si>
+    <t>Condition.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/ediag/r4/CodeSystem/at-ediag-codesystem-business-identifier</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>Condition.identifier:businessIdentifier.value</t>
+  </si>
+  <si>
+    <t>Condition.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>Condition.identifier:businessIdentifier.period</t>
+  </si>
+  <si>
+    <t>Condition.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>Condition.identifier:businessIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>Condition.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>Condition.clinicalStatus</t>
+  </si>
+  <si>
     <t>Klinischer Status der Diagnose (z. B. Status post); mögliche Codes: active | recurrence | relapse | inactive | remission | resolved.</t>
   </si>
   <si>
@@ -562,9 +797,6 @@
   </si>
   <si>
     <t>The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>The clinical status of the condition or diagnosis.</t>
@@ -639,9 +871,6 @@
   </si>
   <si>
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-category|4.0.1</t>
@@ -738,35 +967,7 @@
     <t>Condition.code.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Condition.code.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Condition.code.coding</t>
@@ -1594,12 +1795,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP49"/>
+  <dimension ref="A1:AP58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="30.765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.59765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="30.765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.48828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1616,12 +1817,12 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="73.078125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="51.9140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -3159,16 +3360,14 @@
         <v>21</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="AC13" s="2"/>
       <c r="AD13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>161</v>
@@ -3186,7 +3385,7 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>21</v>
@@ -3195,55 +3394,59 @@
         <v>21</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
       </c>
@@ -3267,13 +3470,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3291,45 +3494,45 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3337,32 +3540,30 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3387,13 +3588,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3411,7 +3612,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3420,47 +3621,47 @@
         <v>91</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -3472,16 +3673,16 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3507,31 +3708,31 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3543,22 +3744,22 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>21</v>
@@ -3566,10 +3767,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3580,30 +3781,32 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>21</v>
       </c>
@@ -3627,13 +3830,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -3651,7 +3854,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3669,41 +3872,41 @@
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>211</v>
+        <v>134</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>214</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>216</v>
+        <v>21</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
@@ -3712,17 +3915,19 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="O18" t="s" s="2">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3747,11 +3952,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y18" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3769,7 +3976,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3784,30 +3991,30 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3815,7 +4022,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
@@ -3827,19 +4034,23 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>228</v>
+        <v>105</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
       </c>
@@ -3848,10 +4059,10 @@
         <v>21</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>21</v>
@@ -3887,7 +4098,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3899,7 +4110,7 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
@@ -3908,10 +4119,10 @@
         <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>21</v>
@@ -3922,21 +4133,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3945,19 +4156,19 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3971,7 +4182,7 @@
         <v>21</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>21</v>
@@ -3995,31 +4206,31 @@
         <v>21</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>21</v>
@@ -4028,10 +4239,10 @@
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>21</v>
+        <v>229</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>21</v>
@@ -4042,10 +4253,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4056,7 +4267,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -4068,20 +4279,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -4129,13 +4336,13 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
@@ -4150,10 +4357,10 @@
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>21</v>
@@ -4164,10 +4371,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4178,7 +4385,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -4190,20 +4397,18 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4251,7 +4456,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4272,10 +4477,10 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>21</v>
@@ -4284,12 +4489,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4297,31 +4502,31 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4347,13 +4552,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>259</v>
+        <v>194</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4371,49 +4576,49 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>21</v>
+        <v>254</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>21</v>
+        <v>255</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>264</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>266</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4426,24 +4631,24 @@
         <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>267</v>
+        <v>201</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4467,13 +4672,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>21</v>
+        <v>265</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4491,45 +4696,45 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>21</v>
+        <v>267</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4549,19 +4754,19 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>276</v>
+        <v>201</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4587,13 +4792,13 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4611,13 +4816,13 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
@@ -4626,19 +4831,19 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>280</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>21</v>
@@ -4646,10 +4851,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4660,7 +4865,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -4669,19 +4874,19 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>285</v>
+        <v>201</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4707,13 +4912,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4731,7 +4936,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4746,64 +4951,64 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM26" t="s" s="2">
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AN26" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" hidden="true">
-      <c r="A27" t="s" s="2">
-        <v>293</v>
-      </c>
       <c r="B27" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>285</v>
+        <v>201</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4827,13 +5032,11 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>21</v>
+        <v>295</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4851,7 +5054,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4860,36 +5063,36 @@
         <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>21</v>
+        <v>296</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>21</v>
+        <v>301</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4897,28 +5100,28 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>285</v>
+        <v>177</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>301</v>
+        <v>178</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>302</v>
+        <v>179</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4969,7 +5172,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4981,7 +5184,7 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
@@ -4990,55 +5193,57 @@
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP28" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AN28" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>306</v>
-      </c>
       <c r="B29" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>307</v>
+        <v>136</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>308</v>
+        <v>184</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5075,31 +5280,31 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>306</v>
+        <v>187</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
@@ -5111,10 +5316,10 @@
         <v>21</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>310</v>
+        <v>181</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>311</v>
+        <v>21</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>21</v>
@@ -5122,10 +5327,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5136,7 +5341,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5148,16 +5353,20 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5205,13 +5414,13 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -5226,13 +5435,13 @@
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>318</v>
+        <v>21</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>21</v>
@@ -5240,10 +5449,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5263,19 +5472,23 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>320</v>
+        <v>177</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5323,31 +5536,31 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AN31" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>21</v>
@@ -5358,10 +5571,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5372,7 +5585,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5381,18 +5594,20 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>229</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5417,13 +5632,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>21</v>
+        <v>327</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5441,79 +5656,79 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>231</v>
+        <v>321</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>232</v>
+        <v>329</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>21</v>
+        <v>330</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>155</v>
+        <v>332</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>136</v>
+        <v>333</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>234</v>
+        <v>334</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5561,34 +5776,34 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>237</v>
+        <v>331</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>232</v>
+        <v>339</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>21</v>
+        <v>340</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>21</v>
@@ -5596,46 +5811,44 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>136</v>
+        <v>342</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5683,34 +5896,34 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>134</v>
+        <v>348</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>21</v>
@@ -5718,10 +5931,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5741,18 +5954,20 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>171</v>
+        <v>351</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5777,13 +5992,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>335</v>
+        <v>21</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5801,7 +6016,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5810,25 +6025,25 @@
         <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>21</v>
+        <v>355</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>338</v>
+        <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>181</v>
+        <v>356</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>224</v>
+        <v>357</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>21</v>
+        <v>358</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>21</v>
@@ -5836,10 +6051,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5850,7 +6065,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -5862,15 +6077,17 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5919,16 +6136,16 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>103</v>
@@ -5943,21 +6160,21 @@
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5965,28 +6182,28 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>171</v>
+        <v>351</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6013,13 +6230,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>348</v>
+        <v>21</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -6037,7 +6254,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6058,24 +6275,24 @@
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>21</v>
+        <v>371</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6083,32 +6300,30 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6157,19 +6372,19 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>354</v>
+        <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>21</v>
@@ -6181,10 +6396,10 @@
         <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>21</v>
@@ -6192,10 +6407,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6215,16 +6430,16 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>228</v>
+        <v>379</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>229</v>
+        <v>380</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>230</v>
+        <v>381</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6275,7 +6490,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>231</v>
+        <v>378</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6287,7 +6502,7 @@
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
@@ -6296,13 +6511,13 @@
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>21</v>
+        <v>382</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>232</v>
+        <v>383</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>21</v>
@@ -6310,21 +6525,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6336,17 +6551,15 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>136</v>
+        <v>386</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>234</v>
+        <v>387</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6395,7 +6608,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>237</v>
+        <v>385</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6407,7 +6620,7 @@
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>142</v>
+        <v>389</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
@@ -6419,7 +6632,7 @@
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>232</v>
+        <v>390</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6430,46 +6643,42 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>329</v>
+        <v>178</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6517,19 +6726,19 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>331</v>
+        <v>180</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
@@ -6541,7 +6750,7 @@
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6552,14 +6761,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6575,18 +6784,20 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>360</v>
+        <v>184</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6611,13 +6822,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>362</v>
+        <v>21</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>363</v>
+        <v>21</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -6635,7 +6846,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>359</v>
+        <v>187</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6644,25 +6855,25 @@
         <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>365</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>366</v>
+        <v>181</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>367</v>
+        <v>21</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>21</v>
@@ -6670,14 +6881,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>21</v>
+        <v>394</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6690,22 +6901,26 @@
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>369</v>
+        <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6753,7 +6968,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>368</v>
+        <v>397</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6762,10 +6977,10 @@
         <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
@@ -6777,10 +6992,10 @@
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>343</v>
+        <v>134</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>367</v>
+        <v>21</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>21</v>
@@ -6788,10 +7003,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6814,13 +7029,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>373</v>
+        <v>201</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6847,13 +7062,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>21</v>
+        <v>402</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -6871,31 +7086,31 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>21</v>
+        <v>403</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>376</v>
+        <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>21</v>
+        <v>404</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>377</v>
+        <v>257</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>378</v>
+        <v>299</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -6906,10 +7121,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6920,7 +7135,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6932,13 +7147,13 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>228</v>
+        <v>406</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>229</v>
+        <v>407</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>230</v>
+        <v>408</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6989,19 +7204,19 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>231</v>
+        <v>405</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>21</v>
+        <v>403</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
@@ -7013,7 +7228,7 @@
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>232</v>
+        <v>409</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7024,21 +7239,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -7050,17 +7265,15 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>136</v>
+        <v>201</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>234</v>
+        <v>411</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7085,43 +7298,43 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>21</v>
+        <v>413</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>21</v>
+        <v>414</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>237</v>
+        <v>410</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
@@ -7133,7 +7346,7 @@
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>232</v>
+        <v>415</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -7144,10 +7357,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>381</v>
+        <v>416</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>381</v>
+        <v>416</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7158,7 +7371,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7167,19 +7380,19 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7229,19 +7442,19 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>103</v>
+        <v>420</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
@@ -7250,10 +7463,10 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
@@ -7264,10 +7477,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7278,7 +7491,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7287,16 +7500,16 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>285</v>
+        <v>177</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>389</v>
+        <v>178</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>390</v>
+        <v>179</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7347,7 +7560,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>391</v>
+        <v>180</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7359,7 +7572,7 @@
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
@@ -7368,10 +7581,10 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>392</v>
+        <v>181</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -7382,21 +7595,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>423</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>423</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7405,18 +7618,20 @@
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>394</v>
+        <v>136</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>395</v>
+        <v>184</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7465,41 +7680,1111 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AG49" t="s" s="2">
+      <c r="AG50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AH49" t="s" s="2">
+      <c r="H53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AI49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
+      <c r="H54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AK49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AK56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AN49" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP49" t="s" s="2">
+      <c r="AN56" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP49">
+  <autoFilter ref="A1:AP58">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7509,7 +8794,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI48">
+  <conditionalFormatting sqref="A2:AI57">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T11:14:45+00:00</t>
+    <t>2026-09-30T12:38:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:38:12+00:00</t>
+    <t>2026-09-30T12:52:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:52:09+00:00</t>
+    <t>2026-09-30T14:46:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T14:46:14+00:00</t>
+    <t>2026-10-01T13:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1059,7 +1059,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
@@ -1183,7 +1183,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitionerRole)
 </t>
   </si>
   <si>
@@ -1202,7 +1202,7 @@
     <t>Condition.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|RelatedPerson)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitionerRole|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient|https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-relatedperson)
 </t>
   </si>
   <si>
@@ -1808,7 +1808,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="213.203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="226.09375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:01:54+00:00</t>
+    <t>2026-10-02T12:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T12:58:24+00:00</t>
+    <t>2026-10-07T14:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T14:48:24+00:00</t>
+    <t>2026-10-08T12:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T12:55:57+00:00</t>
+    <t>2026-10-08T13:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T13:59:28+00:00</t>
+    <t>2026-10-08T14:12:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="463">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T14:12:43+00:00</t>
+    <t>2026-10-08T15:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -275,7 +275,7 @@
   </si>
   <si>
     <t>con-3:Condition.clinicalStatus SHALL be present if verificationStatus is not entered-in-error and category is problem-list-item {clinicalStatus.exists() or verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code = 'entered-in-error').exists() or category.select($this='problem-list-item').empty()}
-con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}condition-status-combination:Erlaubte Kombinationen von clinicalStatus und verificationStatus: active mit provisional, differential oder ohne verificationStatus; inactive mit refuted oder ohne verificationStatus. {verificationStatus.exists() implies ((verificationStatus.coding.exists(code = 'provisional' or code = 'differential') and clinicalStatus.coding.exists(code = 'active')) or (verificationStatus.coding.exists(code = 'refuted') and clinicalStatus.coding.exists(code = 'inactive')))}</t>
   </si>
   <si>
     <t>Event</t>
@@ -790,7 +790,7 @@
     <t>Condition.clinicalStatus</t>
   </si>
   <si>
-    <t>Klinischer Status der Diagnose (z. B. Status post); mögliche Codes: active | recurrence | relapse | inactive | remission | resolved.</t>
+    <t>Klinischer Status der Diagnose (z. B. Status post); mögliche Codes: active | inactive.</t>
   </si>
   <si>
     <t>The clinical status of the condition.</t>
@@ -799,10 +799,7 @@
     <t>The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>The clinical status of the condition or diagnosis.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-clinical|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-condition-clinical-status-vs</t>
   </si>
   <si>
     <t>con-3
@@ -828,7 +825,7 @@
     <t>Condition.verificationStatus</t>
   </si>
   <si>
-    <t>Verifizierungsstatus der Diagnose, mögliche Codes: unconfirmed | provisional | differential | confirmed | refuted | entered-in-error.</t>
+    <t>Verifizierungsstatus der Diagnose, mögliche Codes: provisional | differential | refuted.</t>
   </si>
   <si>
     <t>The verification status to support the clinical status of the condition.</t>
@@ -838,10 +835,7 @@
 The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>The verification status to support or decline the clinical status of the condition or diagnosis.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-ver-status|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-condition-verification-status-vs</t>
   </si>
   <si>
     <t>con-3
@@ -1823,7 +1817,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.9140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.64453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4554,11 +4548,9 @@
       <c r="X23" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Y23" t="s" s="2">
+      <c r="Y23" s="2"/>
+      <c r="Z23" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4585,25 +4577,25 @@
         <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>21</v>
@@ -4611,10 +4603,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4622,7 +4614,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>91</v>
@@ -4640,13 +4632,13 @@
         <v>201</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4674,11 +4666,9 @@
       <c r="X24" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Y24" t="s" s="2">
-        <v>264</v>
-      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4696,7 +4686,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4705,36 +4695,36 @@
         <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>270</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4760,13 +4750,13 @@
         <v>201</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4795,11 +4785,11 @@
         <v>206</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
       </c>
@@ -4816,7 +4806,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4834,16 +4824,16 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>21</v>
@@ -4851,10 +4841,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4880,13 +4870,13 @@
         <v>201</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4915,11 +4905,11 @@
         <v>115</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>284</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4936,7 +4926,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4954,31 +4944,31 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>289</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5000,14 +4990,14 @@
         <v>201</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5036,7 +5026,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -5054,7 +5044,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5069,30 +5059,30 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>301</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5207,10 +5197,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5327,10 +5317,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5353,19 +5343,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5414,7 +5404,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5435,10 +5425,10 @@
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>21</v>
@@ -5449,10 +5439,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5478,16 +5468,16 @@
         <v>177</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5536,7 +5526,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5557,10 +5547,10 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>21</v>
@@ -5571,10 +5561,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5600,13 +5590,13 @@
         <v>201</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5632,14 +5622,14 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Y32" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5656,7 +5646,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5674,31 +5664,31 @@
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5717,17 +5707,17 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5776,7 +5766,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>91</v>
@@ -5791,19 +5781,19 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>21</v>
@@ -5811,10 +5801,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5837,16 +5827,16 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5896,7 +5886,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5911,19 +5901,19 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>21</v>
@@ -5931,10 +5921,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5957,16 +5947,16 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6016,7 +6006,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6031,19 +6021,19 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>21</v>
@@ -6051,10 +6041,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6077,16 +6067,16 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6136,7 +6126,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6145,7 +6135,7 @@
         <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>103</v>
@@ -6160,10 +6150,10 @@
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>21</v>
@@ -6171,10 +6161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6197,13 +6187,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6254,7 +6244,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6275,13 +6265,13 @@
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>21</v>
@@ -6289,10 +6279,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6315,13 +6305,13 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6372,7 +6362,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6396,10 +6386,10 @@
         <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>21</v>
@@ -6407,10 +6397,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6433,13 +6423,13 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6490,7 +6480,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6511,13 +6501,13 @@
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>21</v>
@@ -6525,10 +6515,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6551,13 +6541,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6608,7 +6598,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6620,7 +6610,7 @@
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
@@ -6632,7 +6622,7 @@
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6643,10 +6633,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6761,10 +6751,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6881,14 +6871,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6910,10 +6900,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>158</v>
@@ -6968,7 +6958,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7003,10 +6993,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7032,10 +7022,10 @@
         <v>201</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7062,13 +7052,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -7086,7 +7076,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7095,7 +7085,7 @@
         <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>103</v>
@@ -7104,13 +7094,13 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7121,10 +7111,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7147,13 +7137,13 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7204,7 +7194,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7213,7 +7203,7 @@
         <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>103</v>
@@ -7228,7 +7218,7 @@
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7239,10 +7229,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7268,10 +7258,10 @@
         <v>201</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7298,13 +7288,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7322,7 +7312,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7346,7 +7336,7 @@
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -7357,10 +7347,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7383,16 +7373,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7442,7 +7432,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7454,7 +7444,7 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
@@ -7466,7 +7456,7 @@
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
@@ -7477,10 +7467,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7595,10 +7585,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7715,14 +7705,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7744,10 +7734,10 @@
         <v>136</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>158</v>
@@ -7802,7 +7792,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7837,10 +7827,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7866,10 +7856,10 @@
         <v>201</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7896,13 +7886,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -7920,7 +7910,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7929,25 +7919,25 @@
         <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>21</v>
@@ -7955,10 +7945,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7981,13 +7971,13 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8038,7 +8028,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8047,7 +8037,7 @@
         <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>103</v>
@@ -8062,10 +8052,10 @@
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>21</v>
@@ -8073,10 +8063,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8099,13 +8089,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8156,7 +8146,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8171,16 +8161,16 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -8191,10 +8181,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8309,10 +8299,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8429,10 +8419,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8455,16 +8445,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8514,7 +8504,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8538,7 +8528,7 @@
         <v>134</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -8549,10 +8539,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8575,13 +8565,13 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8632,7 +8622,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8656,7 +8646,7 @@
         <v>134</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -8667,10 +8657,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8693,13 +8683,13 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8750,7 +8740,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>91</v>
@@ -8774,7 +8764,7 @@
         <v>134</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T15:20:56+00:00</t>
+    <t>2026-10-09T06:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T06:09:27+00:00</t>
+    <t>2026-10-09T08:15:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:15:54+00:00</t>
+    <t>2026-10-09T08:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1373,11 +1373,8 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.Minimal.DocumentReference)
 </t>
-  </si>
-  <si>
-    <t>Supporting information found elsewhere</t>
   </si>
   <si>
     <t>Links to other relevant information, including pathology reports.</t>
@@ -7974,10 +7971,10 @@
         <v>433</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8063,10 +8060,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8089,13 +8086,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8146,7 +8143,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8161,16 +8158,16 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -8181,10 +8178,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8299,10 +8296,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8419,10 +8416,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8445,16 +8442,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8504,7 +8501,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8528,7 +8525,7 @@
         <v>134</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -8539,10 +8536,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8568,10 +8565,10 @@
         <v>349</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8622,7 +8619,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8646,7 +8643,7 @@
         <v>134</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -8657,10 +8654,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8683,13 +8680,13 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8740,7 +8737,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>91</v>
@@ -8764,7 +8761,7 @@
         <v>134</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:42:14+00:00</t>
+    <t>2026-10-09T09:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:07:37+00:00</t>
+    <t>2026-10-09T12:41:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T12:41:54+00:00</t>
+    <t>2026-10-12T13:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:54:53+00:00</t>
+    <t>2026-10-12T14:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:06:36+00:00</t>
+    <t>2026-10-12T14:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:31:02+00:00</t>
+    <t>2026-10-13T07:15:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T07:15:40+00:00</t>
+    <t>2026-10-14T06:31:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T06:31:33+00:00</t>
+    <t>2026-10-15T07:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T07:03:41+00:00</t>
+    <t>2026-10-16T09:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3293,7 +3293,7 @@
         <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>21</v>
@@ -3394,7 +3394,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>171</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>21</v>
@@ -3772,7 +3772,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -4000,7 +4000,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>211</v>
       </c>
@@ -4019,7 +4019,7 @@
         <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
@@ -4122,7 +4122,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>222</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>21</v>
